--- a/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20231.xlsx
+++ b/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20231.xlsx
@@ -530,16 +530,19 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>83.33</v>
+      </c>
+      <c r="H2">
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -595,16 +598,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>87.5</v>
+        <v>83.33</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20231.xlsx
+++ b/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20231.xlsx
@@ -598,16 +598,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>83.33</v>
+        <v>87.5</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20231.xlsx
+++ b/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20231.xlsx
@@ -607,7 +607,7 @@
         <v>87.5</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>9.4</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20231.xlsx
+++ b/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20231.xlsx
@@ -607,7 +607,7 @@
         <v>87.5</v>
       </c>
       <c r="H2">
-        <v>9.4</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
